--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -456,23 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.14062</v>
+        <v>17.79171</v>
       </c>
       <c r="D2" t="n">
-        <v>17.65158</v>
+        <v>16.84264</v>
       </c>
       <c r="E2" t="n">
-        <v>17.45471</v>
+        <v>17.38055</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.08694</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05262</v>
+        <v>23.34559</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89192</v>
+        <v>36.16811</v>
       </c>
     </row>
     <row r="3">
@@ -482,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.54001</v>
+        <v>17.60742</v>
       </c>
       <c r="D3" t="n">
-        <v>17.58882</v>
+        <v>16.6894</v>
       </c>
       <c r="E3" t="n">
-        <v>17.19053</v>
+        <v>16.87104</v>
       </c>
       <c r="F3" t="n">
-        <v>45.27837</v>
+        <v>22.6345</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>22.85639</v>
       </c>
       <c r="H3" t="n">
-        <v>1.90175</v>
+        <v>35.81918</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +509,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="C4" t="n">
+        <v>17.30308</v>
       </c>
       <c r="D4" t="n">
-        <v>17.22111</v>
+        <v>16.50573</v>
       </c>
       <c r="E4" t="n">
-        <v>17.30824</v>
+        <v>17.17639</v>
       </c>
       <c r="F4" t="n">
-        <v>43.9175</v>
+        <v>22.69572</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05269</v>
+        <v>22.66495</v>
       </c>
       <c r="H4" t="n">
-        <v>1.90195</v>
+        <v>35.78772</v>
       </c>
     </row>
     <row r="5">
@@ -533,25 +534,23 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>17.59803</v>
       </c>
       <c r="D5" t="n">
-        <v>17.06789</v>
+        <v>16.97833</v>
       </c>
       <c r="E5" t="n">
-        <v>17.59539</v>
+        <v>17.07062</v>
       </c>
       <c r="F5" t="n">
-        <v>45.52254</v>
+        <v>22.60846</v>
       </c>
       <c r="G5" t="n">
-        <v>0.053</v>
+        <v>22.91098</v>
       </c>
       <c r="H5" t="n">
-        <v>1.88389</v>
+        <v>35.92539</v>
       </c>
     </row>
     <row r="6">
@@ -561,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.71951</v>
+        <v>17.65034</v>
       </c>
       <c r="D6" t="n">
-        <v>17.05091</v>
+        <v>16.83447</v>
       </c>
       <c r="E6" t="n">
-        <v>17.58394</v>
+        <v>17.36289</v>
       </c>
       <c r="F6" t="n">
-        <v>44.72521</v>
+        <v>22.48978</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05347</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#DIV/0!</v>
+        <v>22.98771</v>
+      </c>
+      <c r="H6" t="n">
+        <v>35.89406</v>
       </c>
     </row>
     <row r="7">
@@ -586,24 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.09556</v>
+        <v>17.3158</v>
       </c>
       <c r="D7" t="n">
-        <v>17.00296</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 16.48 </t>
-        </is>
+        <v>16.21321</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.03896</v>
       </c>
       <c r="F7" t="n">
-        <v>44.50184</v>
+        <v>22.47708</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05419</v>
+        <v>23.12446</v>
       </c>
       <c r="H7" t="n">
-        <v>1.90234</v>
+        <v>36.44897</v>
       </c>
     </row>
     <row r="8">
@@ -613,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.23768</v>
+        <v>18.22702</v>
       </c>
       <c r="D8" t="n">
-        <v>17.34028</v>
+        <v>16.89211</v>
       </c>
       <c r="E8" t="n">
-        <v>17.61692</v>
+        <v>17.24391</v>
       </c>
       <c r="F8" t="n">
-        <v>44.13519</v>
+        <v>22.91361</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05173</v>
+        <v>22.78194</v>
       </c>
       <c r="H8" t="n">
-        <v>1.91507</v>
+        <v>36.54334</v>
       </c>
     </row>
     <row r="9">
@@ -638,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.63201</v>
+        <v>17.68898</v>
       </c>
       <c r="D9" t="n">
-        <v>17.59186</v>
+        <v>16.68596</v>
       </c>
       <c r="E9" t="n">
-        <v>17.43846</v>
+        <v>17.10038</v>
       </c>
       <c r="F9" t="n">
-        <v>43.96718</v>
+        <v>23.36407</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05247</v>
+        <v>22.77206</v>
       </c>
       <c r="H9" t="n">
-        <v>1.95023</v>
+        <v>36.28421</v>
       </c>
     </row>
     <row r="10">
@@ -663,156 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.60088</v>
+        <v>17.59885</v>
       </c>
       <c r="D10" t="n">
-        <v>17.33269</v>
+        <v>16.56242</v>
       </c>
       <c r="E10" t="n">
-        <v>17.40882</v>
+        <v>17.21486</v>
       </c>
       <c r="F10" t="n">
-        <v>45.02515</v>
+        <v>22.58953</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05402</v>
+        <v>22.96963</v>
       </c>
       <c r="H10" t="n">
-        <v>1.92874</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.15326</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.16482</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.17861</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.17627</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.15417</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.16925</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.16606</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.15977</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.14421</v>
+        <v>36.25955</v>
       </c>
     </row>
   </sheetData>
